--- a/180/food/2026-01-29-sm.xlsx
+++ b/180/food/2026-01-29-sm.xlsx
@@ -403,6 +403,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -413,12 +419,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -860,7 +860,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>29.01.2026</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Рис припущенный №305</t>
+          <t>Рис припущенный</t>
         </is>
       </c>
       <c r="E4" s="21" t="n">
@@ -963,35 +963,15 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="25" t="e"/>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>гор.блюдо</t>
-        </is>
-      </c>
+      <c r="B5" s="26" t="e"/>
       <c r="C5" s="27" t="e"/>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>Сосиски "Особые халяль"</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="G5" s="44" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="H5" s="44" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I5" s="44" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J5" s="45" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="D5" s="26" t="e"/>
+      <c r="E5" s="28" t="e"/>
+      <c r="F5" s="28" t="e"/>
+      <c r="G5" s="28" t="e"/>
+      <c r="H5" s="28" t="e"/>
+      <c r="I5" s="28" t="e"/>
+      <c r="J5" s="29" t="e"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="25" t="e"/>
@@ -1007,13 +987,13 @@
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Чай с молоком или сливками №378</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="n">
+          <t>Чай с молоком или сливками</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="31" t="n">
         <v>33.04</v>
       </c>
       <c r="G6" s="44" t="n">
@@ -1036,16 +1016,20 @@
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="27" t="e"/>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
         </is>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="31" t="n">
         <v>12.85</v>
       </c>
       <c r="G7" s="44" t="n">
@@ -1075,13 +1059,13 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Яблоко №338</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="n">
+          <t>Яблоко</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="31" t="n">
         <v>18.35</v>
       </c>
       <c r="G8" s="44" t="n">
@@ -1099,27 +1083,51 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="25" t="e"/>
-      <c r="B9" s="26" t="e"/>
-      <c r="C9" s="27" t="e"/>
-      <c r="D9" s="26" t="e"/>
-      <c r="E9" s="32" t="e"/>
-      <c r="F9" s="32" t="e"/>
-      <c r="G9" s="32" t="e"/>
-      <c r="H9" s="32" t="e"/>
-      <c r="I9" s="32" t="e"/>
-      <c r="J9" s="33" t="e"/>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>гор.блюдо</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Сосиски (Особые халяль)</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="25" t="e"/>
       <c r="B10" s="26" t="e"/>
       <c r="C10" s="27" t="e"/>
       <c r="D10" s="26" t="e"/>
-      <c r="E10" s="32" t="e"/>
-      <c r="F10" s="32" t="e"/>
-      <c r="G10" s="32" t="e"/>
-      <c r="H10" s="32" t="e"/>
-      <c r="I10" s="32" t="e"/>
-      <c r="J10" s="33" t="e"/>
+      <c r="E10" s="28" t="e"/>
+      <c r="F10" s="28" t="e"/>
+      <c r="G10" s="28" t="e"/>
+      <c r="H10" s="28" t="e"/>
+      <c r="I10" s="28" t="e"/>
+      <c r="J10" s="29" t="e"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -1148,34 +1156,14 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>Суп гороховый №127</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="G12" s="44" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="H12" s="44" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I12" s="44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J12" s="45" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="C12" s="27" t="e"/>
+      <c r="D12" s="26" t="e"/>
+      <c r="E12" s="28" t="e"/>
+      <c r="F12" s="28" t="e"/>
+      <c r="G12" s="28" t="e"/>
+      <c r="H12" s="28" t="e"/>
+      <c r="I12" s="28" t="e"/>
+      <c r="J12" s="29" t="e"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="e"/>
@@ -1185,29 +1173,13 @@
         </is>
       </c>
       <c r="C13" s="27" t="e"/>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>Котлета куриная</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>90</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="G13" s="44" t="n">
-        <v>281.7</v>
-      </c>
-      <c r="H13" s="44" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I13" s="44" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J13" s="45" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="D13" s="26" t="e"/>
+      <c r="E13" s="28" t="e"/>
+      <c r="F13" s="28" t="e"/>
+      <c r="G13" s="28" t="e"/>
+      <c r="H13" s="28" t="e"/>
+      <c r="I13" s="28" t="e"/>
+      <c r="J13" s="29" t="e"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="25" t="e"/>
@@ -1216,34 +1188,14 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>Картофельное пюре №377</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>150</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>105</v>
-      </c>
-      <c r="H14" s="44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="45" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="C14" s="27" t="e"/>
+      <c r="D14" s="26" t="e"/>
+      <c r="E14" s="28" t="e"/>
+      <c r="F14" s="28" t="e"/>
+      <c r="G14" s="28" t="e"/>
+      <c r="H14" s="28" t="e"/>
+      <c r="I14" s="28" t="e"/>
+      <c r="J14" s="29" t="e"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="25" t="e"/>
@@ -1252,32 +1204,14 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Чай с лимоном №459</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>180</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="G15" s="44" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="H15" s="32" t="e"/>
-      <c r="I15" s="44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J15" s="45" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="C15" s="27" t="e"/>
+      <c r="D15" s="26" t="e"/>
+      <c r="E15" s="28" t="e"/>
+      <c r="F15" s="28" t="e"/>
+      <c r="G15" s="28" t="e"/>
+      <c r="H15" s="28" t="e"/>
+      <c r="I15" s="28" t="e"/>
+      <c r="J15" s="29" t="e"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="25" t="e"/>
@@ -1287,29 +1221,13 @@
         </is>
       </c>
       <c r="C16" s="27" t="e"/>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Хлеб пшеничный</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>80</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>27.73</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>187</v>
-      </c>
-      <c r="H16" s="44" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I16" s="44" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J16" s="45" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="D16" s="26" t="e"/>
+      <c r="E16" s="28" t="e"/>
+      <c r="F16" s="28" t="e"/>
+      <c r="G16" s="28" t="e"/>
+      <c r="H16" s="28" t="e"/>
+      <c r="I16" s="28" t="e"/>
+      <c r="J16" s="29" t="e"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="25" t="e"/>
@@ -1320,24 +1238,24 @@
       </c>
       <c r="C17" s="27" t="e"/>
       <c r="D17" s="26" t="e"/>
-      <c r="E17" s="32" t="e"/>
-      <c r="F17" s="32" t="e"/>
-      <c r="G17" s="32" t="e"/>
-      <c r="H17" s="32" t="e"/>
-      <c r="I17" s="32" t="e"/>
-      <c r="J17" s="33" t="e"/>
+      <c r="E17" s="28" t="e"/>
+      <c r="F17" s="28" t="e"/>
+      <c r="G17" s="28" t="e"/>
+      <c r="H17" s="28" t="e"/>
+      <c r="I17" s="28" t="e"/>
+      <c r="J17" s="29" t="e"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="25" t="e"/>
       <c r="B18" s="26" t="e"/>
       <c r="C18" s="27" t="e"/>
       <c r="D18" s="26" t="e"/>
-      <c r="E18" s="32" t="e"/>
-      <c r="F18" s="32" t="e"/>
-      <c r="G18" s="32" t="e"/>
-      <c r="H18" s="32" t="e"/>
-      <c r="I18" s="32" t="e"/>
-      <c r="J18" s="33" t="e"/>
+      <c r="E18" s="28" t="e"/>
+      <c r="F18" s="28" t="e"/>
+      <c r="G18" s="28" t="e"/>
+      <c r="H18" s="28" t="e"/>
+      <c r="I18" s="28" t="e"/>
+      <c r="J18" s="29" t="e"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="e"/>
